--- a/server/data/reports/snehal_harde2935_gmail_com/Selected_Candidates_2026-10-12.xlsx
+++ b/server/data/reports/snehal_harde2935_gmail_com/Selected_Candidates_2026-10-12.xlsx
@@ -16,7 +16,7 @@
     <t>AvaHire AI - Daily Selected Candidates Report (12-Oct-2026)</t>
   </si>
   <si>
-    <t>Selection Date: 12-Oct-2026  |  Total Selected: 9 Selected Candidates  |  Generated: 12/10/2026, 13:19:07</t>
+    <t>Selection Date: 12-Oct-2026  |  Total Selected: 9 Selected Candidates  |  Generated: 12/10/2026, 19:46:51</t>
   </si>
   <si>
     <t>Sr. No.</t>
@@ -58,7 +58,7 @@
     <t>User 2 Selected Candidate</t>
   </si>
   <si>
-    <t>u2.sel.1791791335272@test.com</t>
+    <t>u2.sel.1791814605695@test.com</t>
   </si>
   <si>
     <t>N/A</t>
@@ -70,7 +70,7 @@
     <t>Infrastructure</t>
   </si>
   <si>
-    <t>12 Oct 2026, 13:19</t>
+    <t>12 Oct 2026, 19:46</t>
   </si>
   <si>
     <t>12-Oct-2026</t>
